--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.25486213172563</v>
+        <v>1.666415096405415</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06511778177717</v>
+        <v>1.79808163953879</v>
       </c>
       <c r="E2" t="n">
-        <v>42.6448478592945</v>
+        <v>6.929787777135357</v>
       </c>
       <c r="F2" t="n">
-        <v>39.09370251362616</v>
+        <v>6.35272665846425</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>95.54455785031463</v>
+        <v>15.52599065067613</v>
       </c>
       <c r="D3" t="n">
-        <v>89.25252280902947</v>
+        <v>14.50353495646729</v>
       </c>
       <c r="E3" t="n">
-        <v>42.6448478592945</v>
+        <v>6.929787777135357</v>
       </c>
       <c r="F3" t="n">
-        <v>39.09370251362616</v>
+        <v>6.35272665846425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
